--- a/urunler.xlsx
+++ b/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\US\Nuri\katalog-tasarim-v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD9937E-29D4-4D64-B0D2-9B8515BB39F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B63358-45F1-4EA4-9C30-F0ACD6E24C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1860" yWindow="1425" windowWidth="28800" windowHeight="14580" xr2:uid="{829A082B-4BA8-44C9-B291-ABAF2D9932FE}"/>
+    <workbookView xWindow="0" yWindow="900" windowWidth="28800" windowHeight="14580" xr2:uid="{829A082B-4BA8-44C9-B291-ABAF2D9932FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="6" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="194">
   <si>
     <t>POS</t>
   </si>
@@ -555,15 +555,9 @@
     <t>ANGSET20</t>
   </si>
   <si>
-    <t>Kein Verkauf Flayer Set Menüteller</t>
-  </si>
-  <si>
     <t>ANGSET21</t>
   </si>
   <si>
-    <t>Kein Verkauf Flayer Set Besteck</t>
-  </si>
-  <si>
     <t>ANGSET22</t>
   </si>
   <si>
@@ -577,9 +571,6 @@
   </si>
   <si>
     <t>ANGSET25</t>
-  </si>
-  <si>
-    <t>Kein Verkauf Flayer Set Sprehe</t>
   </si>
   <si>
     <t>ANGSET29</t>
@@ -1032,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD9F8F7-F2F7-4142-ABCD-CA189EEC430E}">
-  <dimension ref="A1:P114"/>
+  <dimension ref="A1:P112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
@@ -1066,13 +1057,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>5</v>
@@ -1116,12 +1107,6 @@
         <f>C2&amp;".psd"</f>
         <v>16542.psd</v>
       </c>
-      <c r="O2" t="s">
-        <v>156</v>
-      </c>
-      <c r="P2" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1152,12 +1137,6 @@
         <f t="shared" ref="J3:J10" si="0">C3&amp;".psd"</f>
         <v>235.psd</v>
       </c>
-      <c r="O3" t="s">
-        <v>158</v>
-      </c>
-      <c r="P3" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -1188,12 +1167,6 @@
         <f t="shared" si="0"/>
         <v>213N.psd</v>
       </c>
-      <c r="O4" t="s">
-        <v>160</v>
-      </c>
-      <c r="P4" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -1224,12 +1197,6 @@
         <f t="shared" si="0"/>
         <v>ANGSET28.psd</v>
       </c>
-      <c r="O5" t="s">
-        <v>162</v>
-      </c>
-      <c r="P5" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -1260,12 +1227,6 @@
         <f t="shared" si="0"/>
         <v>216F.psd</v>
       </c>
-      <c r="O6" t="s">
-        <v>164</v>
-      </c>
-      <c r="P6" t="s">
-        <v>165</v>
-      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -1296,12 +1257,6 @@
         <f t="shared" si="0"/>
         <v>156B.psd</v>
       </c>
-      <c r="O7" t="s">
-        <v>166</v>
-      </c>
-      <c r="P7" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -1332,12 +1287,6 @@
         <f t="shared" si="0"/>
         <v>102M.psd</v>
       </c>
-      <c r="O8" t="s">
-        <v>168</v>
-      </c>
-      <c r="P8" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1368,12 +1317,6 @@
         <f>C9&amp;".psd"</f>
         <v>555.psd</v>
       </c>
-      <c r="O9" t="s">
-        <v>170</v>
-      </c>
-      <c r="P9" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -1404,12 +1347,6 @@
         <f t="shared" si="0"/>
         <v>330F.psd</v>
       </c>
-      <c r="O10" t="s">
-        <v>172</v>
-      </c>
-      <c r="P10" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -1440,12 +1377,6 @@
         <f>C11&amp;".psd"</f>
         <v>330C.psd</v>
       </c>
-      <c r="O11" t="s">
-        <v>174</v>
-      </c>
-      <c r="P11" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -1476,12 +1407,6 @@
         <f t="shared" ref="J12:J72" si="1">C12&amp;".psd"</f>
         <v>ANGSET24.psd</v>
       </c>
-      <c r="O12" t="s">
-        <v>176</v>
-      </c>
-      <c r="P12" t="s">
-        <v>177</v>
-      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -1512,12 +1437,6 @@
         <f t="shared" si="1"/>
         <v>ANGSET16.psd</v>
       </c>
-      <c r="O13" t="s">
-        <v>178</v>
-      </c>
-      <c r="P13" t="s">
-        <v>179</v>
-      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -1548,12 +1467,6 @@
         <f t="shared" si="1"/>
         <v>ANGSET26.psd</v>
       </c>
-      <c r="O14" t="s">
-        <v>180</v>
-      </c>
-      <c r="P14" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -1584,12 +1497,6 @@
         <f t="shared" si="1"/>
         <v>ANGSET12.psd</v>
       </c>
-      <c r="O15" t="s">
-        <v>182</v>
-      </c>
-      <c r="P15" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -1620,14 +1527,8 @@
         <f t="shared" si="1"/>
         <v>ANGSET27.psd</v>
       </c>
-      <c r="O16" t="s">
-        <v>184</v>
-      </c>
-      <c r="P16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1656,14 +1557,8 @@
         <f t="shared" si="1"/>
         <v>275B.psd</v>
       </c>
-      <c r="O17" t="s">
-        <v>185</v>
-      </c>
-      <c r="P17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1692,14 +1587,8 @@
         <f t="shared" si="1"/>
         <v>431A.psd</v>
       </c>
-      <c r="O18" t="s">
-        <v>186</v>
-      </c>
-      <c r="P18" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1728,14 +1617,8 @@
         <f t="shared" si="1"/>
         <v>324.psd</v>
       </c>
-      <c r="O19" t="s">
-        <v>187</v>
-      </c>
-      <c r="P19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1764,14 +1647,8 @@
         <f t="shared" si="1"/>
         <v>131.psd</v>
       </c>
-      <c r="O20" t="s">
-        <v>188</v>
-      </c>
-      <c r="P20" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1800,14 +1677,8 @@
         <f t="shared" si="1"/>
         <v>182L.psd</v>
       </c>
-      <c r="O21" t="s">
-        <v>189</v>
-      </c>
-      <c r="P21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1837,7 +1708,7 @@
         <v>323.psd</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1867,7 +1738,7 @@
         <v>234H.psd</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1897,7 +1768,7 @@
         <v>229S.psd</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1927,7 +1798,7 @@
         <v>330.psd</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1957,7 +1828,7 @@
         <v>183.psd</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1987,7 +1858,7 @@
         <v>522.psd</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2017,7 +1888,7 @@
         <v>325M.psd</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2047,7 +1918,7 @@
         <v>88.psd</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2077,7 +1948,7 @@
         <v>229F.psd</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2107,7 +1978,7 @@
         <v>229FR.psd</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2142,10 +2013,10 @@
         <v>32</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E33">
         <v>844</v>
@@ -2685,7 +2556,7 @@
         <v>172</v>
       </c>
       <c r="D51" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E51">
         <v>490</v>
@@ -3252,10 +3123,10 @@
         <v>69</v>
       </c>
       <c r="C70" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D70" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E70">
         <v>378</v>
@@ -3282,10 +3153,10 @@
         <v>70</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D71" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E71">
         <v>373</v>
@@ -3363,7 +3234,7 @@
         <v>69</v>
       </c>
       <c r="J73" t="str">
-        <f t="shared" ref="J73:J114" si="2">C73&amp;".psd"</f>
+        <f t="shared" ref="J73:J112" si="2">C73&amp;".psd"</f>
         <v>211S.psd</v>
       </c>
     </row>
@@ -4179,22 +4050,22 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D105" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J105" t="str">
         <f t="shared" si="2"/>
-        <v>ANGSET20.psd</v>
+        <v>ANGSET22.psd</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s">
         <v>176</v>
@@ -4204,125 +4075,95 @@
       </c>
       <c r="J106" t="str">
         <f t="shared" si="2"/>
-        <v>ANGSET22.psd</v>
+        <v>ANGSET23.psd</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J107" t="str">
         <f t="shared" si="2"/>
-        <v>ANGSET23.psd</v>
+        <v>ANGSET30.psd</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" t="s">
         <v>180</v>
-      </c>
-      <c r="D108" t="s">
-        <v>181</v>
       </c>
       <c r="J108" t="str">
         <f t="shared" si="2"/>
-        <v>ANGSET25.psd</v>
+        <v>ANGSET31.psd</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C109" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J109" t="str">
         <f t="shared" si="2"/>
-        <v>ANGSET30.psd</v>
+        <v>ANGSET32.psd</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C110" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J110" t="str">
         <f t="shared" si="2"/>
-        <v>ANGSET31.psd</v>
+        <v>ANGSET33.psd</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D111" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J111" t="str">
         <f t="shared" si="2"/>
-        <v>ANGSET32.psd</v>
+        <v>ANGSET34.psd</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C112" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D112" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J112" t="str">
-        <f t="shared" si="2"/>
-        <v>ANGSET33.psd</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="C113" t="s">
-        <v>188</v>
-      </c>
-      <c r="D113" t="s">
-        <v>183</v>
-      </c>
-      <c r="J113" t="str">
-        <f t="shared" si="2"/>
-        <v>ANGSET34.psd</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="C114" t="s">
-        <v>189</v>
-      </c>
-      <c r="D114" t="s">
-        <v>183</v>
-      </c>
-      <c r="J114" t="str">
         <f t="shared" si="2"/>
         <v>ANGSET35.psd</v>
       </c>
